--- a/data/trending_integrated_20261028_13.xlsx
+++ b/data/trending_integrated_20261028_13.xlsx
@@ -584,7 +584,7 @@
         <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>150529534401</v>
+        <v>150681821291</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -619,7 +619,7 @@
         <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>647000</v>
+        <v>1208000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18940</v>
+        <v>19620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.65%</t>
+          <t>'+23.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -693,7 +693,7 @@
         <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>19440</v>
+        <v>19800</v>
       </c>
       <c r="M3" t="n">
         <v>15830</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>288952387375</v>
+        <v>302568832750</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -711,14 +711,14 @@
         <v>11550</v>
       </c>
       <c r="R3" t="n">
-        <v>-21000</v>
+        <v>-84000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 기대. 3조 밸류에이션 주장 및 10만 멜콘 목표.</t>
+          <t>미국 마이크론과의 협력 및 반도체 장비 공급망 진입을 근거로 한 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체 장비', '공급망']</t>
+          <t>['마이크론 협력', '반도체 장비']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27800</v>
+        <v>27825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.05%</t>
+          <t>'+17.16%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>163039700900</v>
+        <v>164732924450</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -803,10 +803,10 @@
         <v>13210</v>
       </c>
       <c r="R4" t="n">
-        <v>-35000</v>
+        <v>6000</v>
       </c>
       <c r="S4" t="n">
-        <v>126000</v>
+        <v>227000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>189500</v>
+        <v>189700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.75%</t>
+          <t>'+10.87%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>603688228200</v>
+        <v>615835558650</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -895,23 +895,23 @@
         <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>654000</v>
+        <v>1006000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자우, 숏 스퀴즈 기대감 및 실적 발표 중요성 부각. 배당 및 자사주 매입 관련 논의.</t>
+          <t>우선주 소각 및 자사주 매입 기대감과 함께 향후 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적 발표', '자사주 매입']</t>
+          <t>['우선주 소각', '자사주 매입']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1481000</v>
+        <v>1479000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.44%</t>
+          <t>'+10.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>512</v>
       </c>
       <c r="G6" t="n">
-        <v>1711</v>
+        <v>1718</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>3910274216500</v>
+        <v>3983052236000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -987,10 +987,10 @@
         <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>53000</v>
+        <v>120000</v>
       </c>
       <c r="S6" t="n">
-        <v>55000</v>
+        <v>228000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8950</v>
+        <v>15000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.15%</t>
+          <t>'+9.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>75</v>
+        <v>559</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42</v>
+        <v>2.87</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8200</v>
+        <v>13700</v>
       </c>
       <c r="K7" t="n">
-        <v>8230</v>
+        <v>14210</v>
       </c>
       <c r="L7" t="n">
-        <v>9780</v>
+        <v>15290</v>
       </c>
       <c r="M7" t="n">
-        <v>8100</v>
+        <v>14210</v>
       </c>
       <c r="N7" t="n">
-        <v>1.15</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>114883493745</v>
+        <v>160209320160</v>
       </c>
       <c r="P7" t="n">
-        <v>9820</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2965</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>-63000</v>
+        <v>294000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안 테마 강화 및 AI 관련 호재 발생, 공급 계약 등 객관적 사실에 기반한 주가 상승 기대감이 높아짐.</t>
+          <t>미래 기술 전략 발표와 메타 유리기판, 해상광통신 케이블 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안 테마', 'AI']</t>
+          <t>['미래 기술', '광통신 케이블']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G8" t="n">
-        <v>1641</v>
+        <v>1660</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2612219254750</v>
+        <v>2667133345250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1171,23 +1171,23 @@
         <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>1304000</v>
+        <v>1368000</v>
       </c>
       <c r="S8" t="n">
-        <v>524000</v>
+        <v>1139000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>긍정적 기대감 속에서 투자자들의 관심이 지속되고 있으나, 객관적 사실 기반 분석은 부족함.</t>
+          <t>일부 긍정적인 가격 전망과 함께 군중 심리에 따른 매수 동참 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['증권', '투자']</t>
+          <t>['주가 전망', '매수 심리']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18540</v>
+        <v>8870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+8.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="H9" t="n">
-        <v>4.74</v>
+        <v>1.42</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17090</v>
+        <v>8200</v>
       </c>
       <c r="K9" t="n">
-        <v>19270</v>
+        <v>8230</v>
       </c>
       <c r="L9" t="n">
-        <v>20450</v>
+        <v>9780</v>
       </c>
       <c r="M9" t="n">
-        <v>18070</v>
+        <v>8100</v>
       </c>
       <c r="N9" t="n">
-        <v>4.13</v>
+        <v>1.15</v>
       </c>
       <c r="O9" t="n">
-        <v>44645888225</v>
+        <v>115957114220</v>
       </c>
       <c r="P9" t="n">
-        <v>28600</v>
+        <v>9820</v>
       </c>
       <c r="Q9" t="n">
-        <v>11050</v>
+        <v>2965</v>
       </c>
       <c r="R9" t="n">
-        <v>-34000</v>
+        <v>-67000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 및 AI 관련 공급 계약, 미국 휴머노이드 로봇 시장 성장 등 구체적인 호재와 팩트에 기반한 강력한 주가 상승 전망.</t>
+          <t>미국 보안주 강세 및 AI 데이터센터 공급 계약을 기반으로 한 테마 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['휴머노이드', '공급 계약']</t>
+          <t>['보안 테마', '공급 계약']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14850</v>
+        <v>2650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+8.39%</t>
+          <t>'+8.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="E10" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>551</v>
+        <v>127</v>
       </c>
       <c r="H10" t="n">
-        <v>2.87</v>
+        <v>1.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13700</v>
+        <v>2450</v>
       </c>
       <c r="K10" t="n">
-        <v>14210</v>
+        <v>2525</v>
       </c>
       <c r="L10" t="n">
-        <v>15290</v>
+        <v>2965</v>
       </c>
       <c r="M10" t="n">
-        <v>14210</v>
+        <v>2505</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>157524619065</v>
+        <v>80379780977</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>2965</v>
       </c>
       <c r="Q10" t="n">
-        <v>1760</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>247000</v>
+        <v>-365000</v>
       </c>
       <c r="S10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, 메타 유리 기판 및 해상 광통신 케이블 관련 성장 기대. 외인 프로그램 매수 집중.</t>
+          <t>개인 물량 흡수 및 거래량 증가를 바탕으로 한 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수']</t>
+          <t>['개인 물량 흡수', '거래량 증가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2650</v>
+        <v>18450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+8.16%</t>
+          <t>'+7.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
-        <v>125</v>
+        <v>352</v>
       </c>
       <c r="H11" t="n">
-        <v>1.69</v>
+        <v>4.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2450</v>
+        <v>17090</v>
       </c>
       <c r="K11" t="n">
-        <v>2525</v>
+        <v>19270</v>
       </c>
       <c r="L11" t="n">
-        <v>2965</v>
+        <v>20450</v>
       </c>
       <c r="M11" t="n">
-        <v>2505</v>
+        <v>18070</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>4.13</v>
       </c>
       <c r="O11" t="n">
-        <v>79391094837</v>
+        <v>44991182385</v>
       </c>
       <c r="P11" t="n">
-        <v>2965</v>
+        <v>28600</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>11050</v>
       </c>
       <c r="R11" t="n">
-        <v>181000</v>
+        <v>-55000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>개인 물량 흡수 및 긍정적 거래량 신호 관찰, 주가 상승 기대감 존재하나 구체적인 호재 분석은 미흡.</t>
+          <t>로봇 관련주로서 아틀라스 발주, AI 데이터센터 방열 시스템 공급 계약 등 호재와 함께 최고 실적 전망. 다만, 높은 주가와 물린 투자자 존재로 인한 하방 압력도 언급됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '시세분출']</t>
+          <t>['로봇', 'AI', '카메라 모듈']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19130</v>
+        <v>19200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+6.93%</t>
+          <t>'+7.32%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" t="n">
         <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12" t="n">
         <v>4.25</v>
@@ -1530,7 +1530,7 @@
         <v>3.79</v>
       </c>
       <c r="O12" t="n">
-        <v>63310095315</v>
+        <v>64509530115</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1539,7 +1539,7 @@
         <v>6320</v>
       </c>
       <c r="R12" t="n">
-        <v>22000</v>
+        <v>-23000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64800</v>
+        <v>181000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+3.84%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>113</v>
+        <v>609</v>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="G13" t="n">
-        <v>629</v>
+        <v>2135</v>
       </c>
       <c r="H13" t="n">
-        <v>41.01</v>
+        <v>35.43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62200</v>
+        <v>174300</v>
       </c>
       <c r="K13" t="n">
-        <v>63000</v>
+        <v>181100</v>
       </c>
       <c r="L13" t="n">
-        <v>64800</v>
+        <v>186900</v>
       </c>
       <c r="M13" t="n">
-        <v>62200</v>
+        <v>180000</v>
       </c>
       <c r="N13" t="n">
-        <v>40.44</v>
+        <v>35.49</v>
       </c>
       <c r="O13" t="n">
-        <v>186989893450</v>
+        <v>126030118900</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>304000</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>170900</v>
       </c>
       <c r="R13" t="n">
-        <v>337000</v>
+        <v>-30000</v>
       </c>
       <c r="S13" t="n">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 높은 수익률 달성 및 자사주 매입 관련 긍정적 공시 기반, 향후 주가 상승 기대감 높음.</t>
+          <t>지수 대비 저조한 성과와 외국인/연기금의 매도에 대한 실망감 표출.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '수익률']</t>
+          <t>['지수 대비 저조', '매도세']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>181500</v>
+        <v>64500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+4.13%</t>
+          <t>'+3.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>594</v>
+        <v>123</v>
       </c>
       <c r="F14" t="n">
-        <v>309</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>2020</v>
+        <v>665</v>
       </c>
       <c r="H14" t="n">
-        <v>35.43</v>
+        <v>41.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>174300</v>
+        <v>62200</v>
       </c>
       <c r="K14" t="n">
-        <v>181100</v>
+        <v>63000</v>
       </c>
       <c r="L14" t="n">
-        <v>186900</v>
+        <v>64900</v>
       </c>
       <c r="M14" t="n">
-        <v>180000</v>
+        <v>62200</v>
       </c>
       <c r="N14" t="n">
-        <v>35.49</v>
+        <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>123291144500</v>
+        <v>195625056450</v>
       </c>
       <c r="P14" t="n">
-        <v>304000</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>170900</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>-24000</v>
+        <v>723000</v>
       </c>
       <c r="S14" t="n">
         <v>9000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>매도세 지속 및 주가 부진으로 투자자들의 불만 고조, 객관적 분석 및 명확한 호재 부재.</t>
+          <t>최근 수익률 1위 달성과 자사주 매입 계획을 기반으로 한 긍정적 주가 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['프로그램 매수', '주가 부진']</t>
+          <t>['수익률 1위', '자사주 매입']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30200</v>
+        <v>30100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>27818218925</v>
+        <v>28315684625</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1815,23 +1815,23 @@
         <v>29200</v>
       </c>
       <c r="R15" t="n">
-        <v>120000</v>
+        <v>84000</v>
       </c>
       <c r="S15" t="n">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>거래량 부진 및 지속적인 하락세에 대한 불만. 공매도 및 부정적 이슈 언급. 객관적 근거 부족.</t>
+          <t>카카오의 주가 부진과 네이버 대비 경쟁력 약화에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['하락세', '공매도', '거래량']</t>
+          <t>['주가 부진', '경쟁력 약화']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2195</v>
+        <v>2190</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.15%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.18</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="H16" t="n">
         <v>5.07</v>
@@ -1898,7 +1898,7 @@
         <v>4.89</v>
       </c>
       <c r="O16" t="n">
-        <v>46467653968</v>
+        <v>46744040282</v>
       </c>
       <c r="P16" t="n">
         <v>4980</v>
@@ -1907,7 +1907,7 @@
         <v>774</v>
       </c>
       <c r="R16" t="n">
-        <v>439000</v>
+        <v>-105000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16480</v>
+        <v>16450</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F17" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>39529013755</v>
+        <v>40634745735</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -1999,10 +1999,10 @@
         <v>16270</v>
       </c>
       <c r="R17" t="n">
-        <v>-375000</v>
+        <v>-529000</v>
       </c>
       <c r="S17" t="n">
-        <v>-35000</v>
+        <v>-73000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F18" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G18" t="n">
-        <v>1141</v>
+        <v>1155</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>64540440450</v>
+        <v>65914748050</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2094,7 +2094,7 @@
         <v>-388000</v>
       </c>
       <c r="S18" t="n">
-        <v>-37000</v>
+        <v>-50000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14220</v>
+        <v>14250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.59%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F19" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G19" t="n">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>53734348000</v>
+        <v>55041057305</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2183,23 +2183,23 @@
         <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-569000</v>
+        <v>-873000</v>
       </c>
       <c r="S19" t="n">
-        <v>-46000</v>
+        <v>-85000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 부진과 회사에 대한 부정적 인식으로 투자자들의 불만과 회의감이 고조됨.</t>
+          <t>회사의 경영 상태와 주가에 대한 강한 불만 표출 및 부정적 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상폐', '망했어요']</t>
+          <t>['경영 부실', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-4.08%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>14628880130</v>
+        <v>14757651523</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2275,7 +2275,7 @@
         <v>636</v>
       </c>
       <c r="R20" t="n">
-        <v>-1122000</v>
+        <v>-1333000</v>
       </c>
       <c r="S20" t="n">
         <v>19000</v>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9010</v>
+        <v>9080</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.83</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
         <v>284</v>
@@ -2358,7 +2358,7 @@
         <v>2.63</v>
       </c>
       <c r="O21" t="n">
-        <v>40490428170</v>
+        <v>41312741645</v>
       </c>
       <c r="P21" t="n">
         <v>11690</v>
@@ -2367,10 +2367,10 @@
         <v>2270</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="S21" t="n">
-        <v>-28000</v>
+        <v>-71000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261028_13.xlsx
+++ b/data/trending_integrated_20261028_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>150681821291</v>
+        <v>150838865311</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, 급등세 기록하며 연상 기대감 형성. 과거 쓰레기 회사 이미지 탈피 및 주가 상승 여력 주목.</t>
+          <t>주가 급등에 대한 기대감과 연상 가능성 언급. 과거 부실 기업 이미지에서 벗어나는 모습.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '차트']</t>
+          <t>['급등', '연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19620</v>
+        <v>19400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.94%</t>
+          <t>'+22.55%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G3" t="n">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>302568832750</v>
+        <v>310791981015</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론과의 협력 및 반도체 장비 공급망 진입을 근거로 한 주가 상승 기대.</t>
+          <t>미국 마이크론향 장비 공급 뉴스 기반 급등 기대. 반도체 공급망 진입 및 3조 시총 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론 협력', '반도체 장비']</t>
+          <t>['마이크론', '공급망', '시총']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27825</v>
+        <v>27850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.16%</t>
+          <t>'+17.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>164732924450</v>
+        <v>166277161975</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>189700</v>
+        <v>189000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.87%</t>
+          <t>'+10.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>615835558650</v>
+        <v>623041793450</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>우선주 소각 및 자사주 매입 기대감과 함께 향후 주가 상승 전망.</t>
+          <t>주가 상승 기대감과 실적 발표 및 자사주 매입 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주 소각', '자사주 매입']</t>
+          <t>['실적', '자사주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1479000</v>
+        <v>1475000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.29%</t>
+          <t>'+9.99%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="G6" t="n">
-        <v>1718</v>
+        <v>1786</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>3983052236000</v>
+        <v>4033048738000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>향후 실적 개선 전망 및 시장 동향 분석에 기반한 주가 상승 기대감이 있으나, 구체적인 근거는 일부 부족함.</t>
+          <t>4분기 실적 기대감과 목표가 제시. 외국인 수급 및 시장 전망 긍정적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['4분기 실적', '주가 상승']</t>
+          <t>['실적', '목표가', '외국인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15000</v>
+        <v>14940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.49%</t>
+          <t>'+9.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>160209320160</v>
+        <v>160999257760</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미래 기술 전략 발표와 메타 유리기판, 해상광통신 케이블 관련 긍정적 전망.</t>
+          <t>메타 유리기판, 해상광통신 케이블 등 신규 사업 기대감. 외인 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['미래 기술', '광통신 케이블']</t>
+          <t>['광통신', '유리기판', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241500</v>
+        <v>19470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.78%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.46</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>497</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>1660</v>
+        <v>92</v>
       </c>
       <c r="H8" t="n">
-        <v>46.15</v>
+        <v>4.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>222000</v>
+        <v>17890</v>
       </c>
       <c r="K8" t="n">
-        <v>231000</v>
+        <v>18250</v>
       </c>
       <c r="L8" t="n">
-        <v>243000</v>
+        <v>20000</v>
       </c>
       <c r="M8" t="n">
-        <v>228000</v>
+        <v>17950</v>
       </c>
       <c r="N8" t="n">
-        <v>46.1</v>
+        <v>3.79</v>
       </c>
       <c r="O8" t="n">
-        <v>2667133345250</v>
+        <v>65477397010</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R8" t="n">
-        <v>1368000</v>
+        <v>-23000</v>
       </c>
       <c r="S8" t="n">
-        <v>1139000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일부 긍정적인 가격 전망과 함께 군중 심리에 따른 매수 동참 기대.</t>
+          <t>정부의 양자보안 의무화 발표 및 연이은 해킹 사고 발생으로 보안 섹터 주목. 라온시큐어의 대장 가능성 언급 및 2차 상승 시작점 분석.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 전망', '매수 심리']</t>
+          <t>['양자보안', '해킹', '보안 섹터']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8870</v>
+        <v>241500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.17%</t>
+          <t>'+8.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>78</v>
+        <v>1598</v>
       </c>
       <c r="H9" t="n">
-        <v>1.42</v>
+        <v>46.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8200</v>
+        <v>222000</v>
       </c>
       <c r="K9" t="n">
-        <v>8230</v>
+        <v>231000</v>
       </c>
       <c r="L9" t="n">
-        <v>9780</v>
+        <v>243000</v>
       </c>
       <c r="M9" t="n">
-        <v>8100</v>
+        <v>228000</v>
       </c>
       <c r="N9" t="n">
-        <v>1.15</v>
+        <v>46.1</v>
       </c>
       <c r="O9" t="n">
-        <v>115957114220</v>
+        <v>2712888148750</v>
       </c>
       <c r="P9" t="n">
-        <v>9820</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>2965</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-67000</v>
+        <v>1368000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1139000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 및 AI 데이터센터 공급 계약을 기반으로 한 테마 기대.</t>
+          <t>특정 정치인 언급 및 목표가 제시. 일부 투자자들은 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안 테마', '공급 계약']</t>
+          <t>['정치인', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2650</v>
+        <v>8850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+8.16%</t>
+          <t>'+7.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="H10" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2450</v>
+        <v>8200</v>
       </c>
       <c r="K10" t="n">
-        <v>2525</v>
+        <v>8230</v>
       </c>
       <c r="L10" t="n">
+        <v>9780</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8100</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>117540785195</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9820</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2965</v>
       </c>
-      <c r="M10" t="n">
-        <v>2505</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O10" t="n">
-        <v>80379780977</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2965</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>865</v>
-      </c>
       <c r="R10" t="n">
-        <v>-365000</v>
+        <v>-67000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 물량 흡수 및 거래량 증가를 바탕으로 한 주가 상승 기대감.</t>
+          <t>양자, 보안주 급등 테마와 연관. IT 보안 사고 발생 및 AI 데이터센터 방열 시스템 공급 계약 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['개인 물량 흡수', '거래량 증가']</t>
+          <t>['보안주', 'AI', '공급 계약']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18450</v>
+        <v>18400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+7.96%</t>
+          <t>'+7.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>134</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="H11" t="n">
         <v>4.74</v>
@@ -1438,7 +1438,7 @@
         <v>4.13</v>
       </c>
       <c r="O11" t="n">
-        <v>44991182385</v>
+        <v>45212691485</v>
       </c>
       <c r="P11" t="n">
         <v>28600</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19200</v>
+        <v>2625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+7.32%</t>
+          <t>'+7.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="H12" t="n">
-        <v>4.25</v>
+        <v>1.69</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17890</v>
+        <v>2450</v>
       </c>
       <c r="K12" t="n">
-        <v>18250</v>
+        <v>2525</v>
       </c>
       <c r="L12" t="n">
-        <v>20000</v>
+        <v>2965</v>
       </c>
       <c r="M12" t="n">
-        <v>17950</v>
+        <v>2505</v>
       </c>
       <c r="N12" t="n">
-        <v>3.79</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>64509530115</v>
+        <v>81747185346</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>2965</v>
       </c>
       <c r="Q12" t="n">
-        <v>6320</v>
+        <v>865</v>
       </c>
       <c r="R12" t="n">
-        <v>-23000</v>
+        <v>-365000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>보안 섹터 전반의 강세 및 양자보안 관련 이슈 부각, 단기적 주가 상승 가능성 있으나 추가 근거 필요.</t>
+          <t>거래량 증가와 함께 주가 상승 기대감. 외국인 매수세 및 저평가 의견.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안 섹터', '양자보안']</t>
+          <t>['거래량', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>181000</v>
+        <v>180700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.84%</t>
+          <t>'+3.67%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="F13" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G13" t="n">
-        <v>2135</v>
+        <v>2255</v>
       </c>
       <c r="H13" t="n">
         <v>35.43</v>
@@ -1622,7 +1622,7 @@
         <v>35.49</v>
       </c>
       <c r="O13" t="n">
-        <v>126030118900</v>
+        <v>128848461650</v>
       </c>
       <c r="P13" t="n">
         <v>304000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>지수 대비 저조한 성과와 외국인/연기금의 매도에 대한 실망감 표출.</t>
+          <t>엔비디아의 지분 투자에도 불구하고 외국인, 연기금 매도세 지속. 지수 대비 저조한 흐름과 공매도 비율 증가로 인한 하락 압력 분석.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['지수 대비 저조', '매도세']</t>
+          <t>['외국인 매도', '공매도', '지수 대비']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64500</v>
+        <v>64300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.70%</t>
+          <t>'+3.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>195625056450</v>
+        <v>201635130200</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30100</v>
+        <v>30050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>28315684625</v>
+        <v>28835216800</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>카카오의 주가 부진과 네이버 대비 경쟁력 약화에 대한 불만.</t>
+          <t>카카오 주가 3만원 돌파 시도가 있으나, 거래량 부진 및 네이버 대비 약세 지속. 공매도 지속 및 전반적인 하락 추세 분석.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 부진', '경쟁력 약화']</t>
+          <t>['거래량 부진', '네이버 대비', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,184 +1851,184 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2190</v>
+        <v>16600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="G16" t="n">
-        <v>274</v>
+        <v>332</v>
       </c>
       <c r="H16" t="n">
-        <v>5.07</v>
+        <v>28.03</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2170</v>
+        <v>16390</v>
       </c>
       <c r="K16" t="n">
-        <v>2160</v>
+        <v>16630</v>
       </c>
       <c r="L16" t="n">
-        <v>2475</v>
+        <v>16760</v>
       </c>
       <c r="M16" t="n">
-        <v>2155</v>
+        <v>16300</v>
       </c>
       <c r="N16" t="n">
-        <v>4.89</v>
+        <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>46744040282</v>
+        <v>43666921375</v>
       </c>
       <c r="P16" t="n">
-        <v>4980</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>774</v>
+        <v>16270</v>
       </c>
       <c r="R16" t="n">
-        <v>-105000</v>
+        <v>-529000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-73000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
+          <t>삼성중공업, 주문량 대비 주가 흐름에 대한 불만 제기. 실적 발표 및 외국인/기관 매수세 지속.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
+          <t>['실적', '외국인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16450</v>
+        <v>2190</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.92%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="H17" t="n">
-        <v>28.03</v>
+        <v>5.07</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16390</v>
+        <v>2170</v>
       </c>
       <c r="K17" t="n">
-        <v>16630</v>
+        <v>2160</v>
       </c>
       <c r="L17" t="n">
-        <v>16760</v>
+        <v>2475</v>
       </c>
       <c r="M17" t="n">
-        <v>16300</v>
+        <v>2155</v>
       </c>
       <c r="N17" t="n">
-        <v>27.96</v>
+        <v>4.89</v>
       </c>
       <c r="O17" t="n">
-        <v>40634745735</v>
+        <v>46853079942</v>
       </c>
       <c r="P17" t="n">
-        <v>35350</v>
+        <v>4980</v>
       </c>
       <c r="Q17" t="n">
-        <v>16270</v>
+        <v>774</v>
       </c>
       <c r="R17" t="n">
-        <v>-529000</v>
+        <v>-105000</v>
       </c>
       <c r="S17" t="n">
-        <v>-73000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼성중공업, 주문량 대비 주가 흐름에 대한 불만 제기. 실적 발표 및 외국인/기관 매수세 지속.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '외국인 매수']</t>
+          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52500</v>
+        <v>52900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F18" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G18" t="n">
-        <v>1155</v>
+        <v>1195</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>65914748050</v>
+        <v>69265520100</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 및 외국인 매도세 속에서도 잠수함 건조 제안 등 일부 긍정적 뉴스.</t>
+          <t>주가 하락 및 2분기 실적 부진에 대한 실망감. 자사주 매입 및 증권가 전망 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 발표', '외국인 매도', '잠수함 건조']</t>
+          <t>['실적', '자사주']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14250</v>
+        <v>14240</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G19" t="n">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>55041057305</v>
+        <v>55937294740</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>회사의 경영 상태와 주가에 대한 강한 불만 표출 및 부정적 전망.</t>
+          <t>주가 하락에 대한 불만과 경영진 비판. 상폐 및 부실 기업 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영 부실', '주가 하락']</t>
+          <t>['상폐', '경영진']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,21 +2223,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.08%</t>
+          <t>'-3.84%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
         <v>108</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>14757651523</v>
+        <v>14837040186</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9080</v>
+        <v>9000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-5.56%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H21" t="n">
         <v>3.46</v>
@@ -2358,7 +2358,7 @@
         <v>2.63</v>
       </c>
       <c r="O21" t="n">
-        <v>41312741645</v>
+        <v>42420834005</v>
       </c>
       <c r="P21" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_13.xlsx
+++ b/data/trending_integrated_20261028_13.xlsx
@@ -584,7 +584,7 @@
         <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>150838865311</v>
+        <v>150930899416</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19400</v>
+        <v>18990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.55%</t>
+          <t>'+19.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>310791981015</v>
+        <v>317459893480</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27850</v>
+        <v>27700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.26%</t>
+          <t>'+16.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>166277161975</v>
+        <v>167131445300</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>189000</v>
+        <v>188900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.46%</t>
+          <t>'+10.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
         <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>623041793450</v>
+        <v>629738482400</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 상승 기대감과 실적 발표 및 자사주 매입 관련 언급.</t>
+          <t>우선주 소각 및 실적 발표에 대한 기대감과 함께 외국인 매수세 언급. 긍정적 논조.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '자사주']</t>
+          <t>['우선주 소각', '실적 발표', '외국인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1475000</v>
+        <v>1476000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.99%</t>
+          <t>'+10.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>520</v>
       </c>
       <c r="G6" t="n">
-        <v>1786</v>
+        <v>1815</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4033048738000</v>
+        <v>4086800996000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4분기 실적 기대감과 목표가 제시. 외국인 수급 및 시장 전망 긍정적.</t>
+          <t>4분기 실적 기대감과 함께 주가 200, 300, 470만 원 등 높은 목표가 제시. 외국인 수급 긍정적. 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', '목표가', '외국인']</t>
+          <t>['실적 기대', '주가 상승', '외국인 수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>160999257760</v>
+        <v>162092694630</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>메타 유리기판, 해상광통신 케이블 등 신규 사업 기대감. 외인 프로그램 매수세 유입.</t>
+          <t>국민연금 및 외국인 프로그램 적극 매수 속에서 메타, 광통신 섹터 호재 기반 2만원 돌파 및 2만 이상 분할매수 권유. 공매도 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '유리기판', '외인']</t>
+          <t>['외국인 프로그램', '메타', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19470</v>
+        <v>241250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>498</v>
       </c>
       <c r="G8" t="n">
-        <v>92</v>
+        <v>1699</v>
       </c>
       <c r="H8" t="n">
-        <v>4.25</v>
+        <v>46.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17890</v>
+        <v>222000</v>
       </c>
       <c r="K8" t="n">
-        <v>18250</v>
+        <v>231000</v>
       </c>
       <c r="L8" t="n">
-        <v>20000</v>
+        <v>243000</v>
       </c>
       <c r="M8" t="n">
-        <v>17950</v>
+        <v>228000</v>
       </c>
       <c r="N8" t="n">
-        <v>3.79</v>
+        <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>65477397010</v>
+        <v>2757277771250</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-23000</v>
+        <v>1368000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1139000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정부의 양자보안 의무화 발표 및 연이은 해킹 사고 발생으로 보안 섹터 주목. 라온시큐어의 대장 가능성 언급 및 2차 상승 시작점 분석.</t>
+          <t>긍정적 기대감 속에서 공매도 세력에 대한 언급과 주가 상승 전망이 혼재. 감정적 표현 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '보안 섹터']</t>
+          <t>['성과급', '공매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241500</v>
+        <v>19430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.78%</t>
+          <t>'+8.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>501</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>1598</v>
+        <v>97</v>
       </c>
       <c r="H9" t="n">
-        <v>46.15</v>
+        <v>4.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>222000</v>
+        <v>17890</v>
       </c>
       <c r="K9" t="n">
-        <v>231000</v>
+        <v>18250</v>
       </c>
       <c r="L9" t="n">
-        <v>243000</v>
+        <v>20000</v>
       </c>
       <c r="M9" t="n">
-        <v>228000</v>
+        <v>17950</v>
       </c>
       <c r="N9" t="n">
-        <v>46.1</v>
+        <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>2712888148750</v>
+        <v>66191935775</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>1368000</v>
+        <v>-23000</v>
       </c>
       <c r="S9" t="n">
-        <v>1139000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>특정 정치인 언급 및 목표가 제시. 일부 투자자들은 긍정적 전망.</t>
+          <t>정부 양자보안 의무화 정책 및 해킹 이슈에 따른 보안 섹터 강세 속에서 라온시큐어 대장주 부상 전망. 2차 상승 시작점.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치인', '목표가']</t>
+          <t>['양자보안', '해킹 이슈', '보안 섹터']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8850</v>
+        <v>8890</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.93%</t>
+          <t>'+8.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="n">
         <v>1.42</v>
@@ -1346,7 +1346,7 @@
         <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>117540785195</v>
+        <v>118316856935</v>
       </c>
       <c r="P10" t="n">
         <v>9820</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18400</v>
+        <v>18450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+7.67%</t>
+          <t>'+7.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.61</v>
       </c>
       <c r="E11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="H11" t="n">
         <v>4.74</v>
@@ -1438,7 +1438,7 @@
         <v>4.13</v>
       </c>
       <c r="O11" t="n">
-        <v>45212691485</v>
+        <v>45305896605</v>
       </c>
       <c r="P11" t="n">
         <v>28600</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>로봇 관련주로서 아틀라스 발주, AI 데이터센터 방열 시스템 공급 계약 등 호재와 함께 최고 실적 전망. 다만, 높은 주가와 물린 투자자 존재로 인한 하방 압력도 언급됨.</t>
+          <t>AI 데이터센터 방열 시스템 공급 계약 체결 및 휴머노이드, 로봇 관련 기술 호재 기반 상승 전망. 이재용 방문 및 글로벌 호재 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇', 'AI', '카메라 모듈']</t>
+          <t>['AI 데이터센터', '휴머노이드', '로봇']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2625</v>
+        <v>2590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+7.14%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H12" t="n">
         <v>1.69</v>
@@ -1530,7 +1530,7 @@
         <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>81747185346</v>
+        <v>82814192739</v>
       </c>
       <c r="P12" t="n">
         <v>2965</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 주가 상승 기대감. 외국인 매수세 및 저평가 의견.</t>
+          <t>거래량 증가와 함께 개인 물량 흡수하며 2750원, 3000원 돌파 기대감. 시세 분출 기간 진입 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['거래량', '외국인']</t>
+          <t>['거래량', '개인 물량 흡수', '시세 분출']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180700</v>
+        <v>180600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.67%</t>
+          <t>'+3.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>627</v>
+        <v>666</v>
       </c>
       <c r="F13" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="G13" t="n">
-        <v>2255</v>
+        <v>2357</v>
       </c>
       <c r="H13" t="n">
         <v>35.43</v>
@@ -1622,7 +1622,7 @@
         <v>35.49</v>
       </c>
       <c r="O13" t="n">
-        <v>128848461650</v>
+        <v>132611017650</v>
       </c>
       <c r="P13" t="n">
         <v>304000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>엔비디아의 지분 투자에도 불구하고 외국인, 연기금 매도세 지속. 지수 대비 저조한 흐름과 공매도 비율 증가로 인한 하락 압력 분석.</t>
+          <t>프로그램 매수세 일부 확인되나, 외인·연기금 매도 및 공매도 비율 증가로 주가 상승 동력 부족. 지수 대비 부진.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매도', '공매도', '지수 대비']</t>
+          <t>['프로그램 매수', '외인 매도', '공매도 비율']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64300</v>
+        <v>64400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.38%</t>
+          <t>'+3.54%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
         <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>201635130200</v>
+        <v>205071966000</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>28835216800</v>
+        <v>29229186175</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>카카오 주가 3만원 돌파 시도가 있으나, 거래량 부진 및 네이버 대비 약세 지속. 공매도 지속 및 전반적인 하락 추세 분석.</t>
+          <t>3만원대 돌파 후에도 거래량 부진 및 카카오 공매도 압박으로 인한 하락세 지속. 네이버 대비 열위.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['거래량 부진', '네이버 대비', '공매도']</t>
+          <t>['거래량 부진', '카카오 공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>43666921375</v>
+        <v>45784974635</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1961,10 +1961,10 @@
         <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H17" t="n">
         <v>5.07</v>
@@ -1990,7 +1990,7 @@
         <v>4.89</v>
       </c>
       <c r="O17" t="n">
-        <v>46853079942</v>
+        <v>47099381169</v>
       </c>
       <c r="P17" t="n">
         <v>4980</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52900</v>
+        <v>53050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="F18" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G18" t="n">
-        <v>1195</v>
+        <v>1221</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>69265520100</v>
+        <v>71872537450</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2142,13 +2142,13 @@
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F19" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G19" t="n">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>55937294740</v>
+        <v>56907014350</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2234,13 +2234,13 @@
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
         <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>14837040186</v>
+        <v>14907793342</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9000</v>
+        <v>9050</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.56%</t>
+          <t>'-5.04%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.83</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
         <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H21" t="n">
         <v>3.46</v>
@@ -2358,7 +2358,7 @@
         <v>2.63</v>
       </c>
       <c r="O21" t="n">
-        <v>42420834005</v>
+        <v>42696492210</v>
       </c>
       <c r="P21" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_13.xlsx
+++ b/data/trending_integrated_20261028_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>150930899416</v>
+        <v>151035413646</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18990</v>
+        <v>18920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.96%</t>
+          <t>'+19.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G3" t="n">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>317459893480</v>
+        <v>321518764195</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론향 장비 공급 뉴스 기반 급등 기대. 반도체 공급망 진입 및 3조 시총 전망.</t>
+          <t>미국 마이크론 등 해외 업체와의 공급망 진입 뉴스 기반, 목표가 상향 및 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론', '공급망', '시총']</t>
+          <t>['마이크론', '공급망', '반도체']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27700</v>
+        <v>27650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.63%</t>
+          <t>'+16.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>167131445300</v>
+        <v>168613015950</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -854,13 +854,13 @@
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
         <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>629738482400</v>
+        <v>637824134150</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1476000</v>
+        <v>1465000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.07%</t>
+          <t>'+9.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>520</v>
       </c>
       <c r="G6" t="n">
-        <v>1815</v>
+        <v>1854</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4086800996000</v>
+        <v>4188112386500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4분기 실적 기대감과 함께 주가 200, 300, 470만 원 등 높은 목표가 제시. 외국인 수급 긍정적. 상승 추세 전망.</t>
+          <t>4분기 실적 기대 및 목표 주가 언급, 실적 발표 후에도 상승 전망. 다수 긍정적 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 기대', '주가 상승', '외국인 수급']</t>
+          <t>['실적', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14940</v>
+        <v>14870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.05%</t>
+          <t>'+8.54%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
         <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>162092694630</v>
+        <v>163385627630</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241250</v>
+        <v>240500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.67%</t>
+          <t>'+8.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="G8" t="n">
-        <v>1699</v>
+        <v>1656</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2757277771250</v>
+        <v>2817042470750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>긍정적 기대감 속에서 공매도 세력에 대한 언급과 주가 상승 전망이 혼재. 감정적 표현 다수.</t>
+          <t>이재명 언급 및 목표가 언급, 공매도 관련 논쟁. 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['성과급', '공매도', '주가 전망']</t>
+          <t>['성과급', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19430</v>
+        <v>19300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.61%</t>
+          <t>'+7.88%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H9" t="n">
         <v>4.25</v>
@@ -1254,7 +1254,7 @@
         <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>66191935775</v>
+        <v>66693739425</v>
       </c>
       <c r="P9" t="n">
         <v>22450</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정부 양자보안 의무화 정책 및 해킹 이슈에 따른 보안 섹터 강세 속에서 라온시큐어 대장주 부상 전망. 2차 상승 시작점.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹 이슈', '보안 섹터']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8890</v>
+        <v>18340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+8.41%</t>
+          <t>'+7.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>87</v>
+        <v>366</v>
       </c>
       <c r="H10" t="n">
-        <v>1.42</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8200</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>8230</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>9780</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>8100</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>118316856935</v>
+        <v>45465208445</v>
       </c>
       <c r="P10" t="n">
-        <v>9820</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>2965</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>-67000</v>
+        <v>-55000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>양자, 보안주 급등 테마와 연관. IT 보안 사고 발생 및 AI 데이터센터 방열 시스템 공급 계약 언급.</t>
+          <t>나무가의 로봇 및 AI 관련 사업 기대감 상승. 미국 휴머노이드 폭등, 로봇의 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 긍정적 뉴스 다수 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '공급 계약']</t>
+          <t>['휴머노이드', 'AI', '로봇']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18450</v>
+        <v>8730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+7.96%</t>
+          <t>'+6.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="H11" t="n">
-        <v>4.74</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17090</v>
+        <v>8200</v>
       </c>
       <c r="K11" t="n">
-        <v>19270</v>
+        <v>8230</v>
       </c>
       <c r="L11" t="n">
-        <v>20450</v>
+        <v>9780</v>
       </c>
       <c r="M11" t="n">
-        <v>18070</v>
+        <v>8100</v>
       </c>
       <c r="N11" t="n">
-        <v>4.13</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>45305896605</v>
+        <v>119354198525</v>
       </c>
       <c r="P11" t="n">
-        <v>28600</v>
+        <v>9820</v>
       </c>
       <c r="Q11" t="n">
-        <v>11050</v>
+        <v>2965</v>
       </c>
       <c r="R11" t="n">
-        <v>-55000</v>
+        <v>-67000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 데이터센터 방열 시스템 공급 계약 체결 및 휴머노이드, 로봇 관련 기술 호재 기반 상승 전망. 이재용 방문 및 글로벌 호재 언급.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '휴머노이드', '로봇']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2590</v>
+        <v>2600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+6.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H12" t="n">
         <v>1.69</v>
@@ -1530,7 +1530,7 @@
         <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>82814192739</v>
+        <v>83539941916</v>
       </c>
       <c r="P12" t="n">
         <v>2965</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180600</v>
+        <v>64400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.61%</t>
+          <t>'+3.54%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>666</v>
+        <v>134</v>
       </c>
       <c r="F13" t="n">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>2357</v>
+        <v>678</v>
       </c>
       <c r="H13" t="n">
-        <v>35.43</v>
+        <v>41.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>174300</v>
+        <v>62200</v>
       </c>
       <c r="K13" t="n">
-        <v>181100</v>
+        <v>63000</v>
       </c>
       <c r="L13" t="n">
-        <v>186900</v>
+        <v>64900</v>
       </c>
       <c r="M13" t="n">
-        <v>180000</v>
+        <v>62200</v>
       </c>
       <c r="N13" t="n">
-        <v>35.49</v>
+        <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>132611017650</v>
+        <v>208068656500</v>
       </c>
       <c r="P13" t="n">
-        <v>304000</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>170900</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>-30000</v>
+        <v>723000</v>
       </c>
       <c r="S13" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>프로그램 매수세 일부 확인되나, 외인·연기금 매도 및 공매도 비율 증가로 주가 상승 동력 부족. 지수 대비 부진.</t>
+          <t>최근 수익률 1위 달성과 자사주 매입 계획을 기반으로 한 긍정적 주가 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['프로그램 매수', '외인 매도', '공매도 비율']</t>
+          <t>['수익률 1위', '자사주 매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64400</v>
+        <v>180400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+3.50%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.57</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>686</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="G14" t="n">
-        <v>678</v>
+        <v>2420</v>
       </c>
       <c r="H14" t="n">
-        <v>41.01</v>
+        <v>35.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62200</v>
+        <v>174300</v>
       </c>
       <c r="K14" t="n">
-        <v>63000</v>
+        <v>181100</v>
       </c>
       <c r="L14" t="n">
-        <v>64900</v>
+        <v>186900</v>
       </c>
       <c r="M14" t="n">
-        <v>62200</v>
+        <v>180000</v>
       </c>
       <c r="N14" t="n">
-        <v>40.44</v>
+        <v>35.49</v>
       </c>
       <c r="O14" t="n">
-        <v>205071966000</v>
+        <v>135913647950</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>304000</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>170900</v>
       </c>
       <c r="R14" t="n">
-        <v>723000</v>
+        <v>-30000</v>
       </c>
       <c r="S14" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>최근 수익률 1위 달성과 자사주 매입 계획을 기반으로 한 긍정적 주가 전망.</t>
+          <t>지수 대비 낮은 상승률, 외인/연기금 매도 및 공매도 비율 지적. 부정적 논조.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수익률 1위', '자사주 매입']</t>
+          <t>['공매도', '외인매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30100</v>
+        <v>30050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>29229186175</v>
+        <v>29503584175</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3만원대 돌파 후에도 거래량 부진 및 카카오 공매도 압박으로 인한 하락세 지속. 네이버 대비 열위.</t>
+          <t>카카오 주가 하락 및 변동성에 대한 부정적 전망과 기대감이 혼재. 일부는 3만원 이하 하락을 예상하며 비판적인 태도를 보임.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['거래량 부진', '카카오 공매도', '주가 하락']</t>
+          <t>['물타기', '공매도', '전환사채']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16600</v>
+        <v>16480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+0.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>45784974635</v>
+        <v>48039434055</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성중공업, 주문량 대비 주가 흐름에 대한 불만 제기. 실적 발표 및 외국인/기관 매수세 지속.</t>
+          <t>주문량 대비 주가 하락, 애널리스트 및 증권사 비판. 부정적 논조.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '외국인 매수']</t>
+          <t>['주가', '실적발표']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,175 +1943,175 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2190</v>
+        <v>52600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.92%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.18</v>
+        <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>261</v>
       </c>
       <c r="G17" t="n">
-        <v>274</v>
+        <v>1228</v>
       </c>
       <c r="H17" t="n">
-        <v>5.07</v>
+        <v>10.31</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2170</v>
+        <v>53000</v>
       </c>
       <c r="K17" t="n">
-        <v>2160</v>
+        <v>53400</v>
       </c>
       <c r="L17" t="n">
-        <v>2475</v>
+        <v>53800</v>
       </c>
       <c r="M17" t="n">
-        <v>2155</v>
+        <v>51200</v>
       </c>
       <c r="N17" t="n">
-        <v>4.89</v>
+        <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>47099381169</v>
+        <v>74616518850</v>
       </c>
       <c r="P17" t="n">
-        <v>4980</v>
+        <v>154800</v>
       </c>
       <c r="Q17" t="n">
-        <v>774</v>
+        <v>51200</v>
       </c>
       <c r="R17" t="n">
-        <v>-105000</v>
+        <v>-388000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
+          <t>주가 하락 및 2분기 실적 부진에 대한 실망감. 자사주 매입 및 증권가 전망 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
+          <t>['실적', '자사주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>042660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53050</v>
+        <v>2145</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="E18" t="n">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
-        <v>260</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>1221</v>
+        <v>279</v>
       </c>
       <c r="H18" t="n">
-        <v>10.31</v>
+        <v>5.07</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>53000</v>
+        <v>2170</v>
       </c>
       <c r="K18" t="n">
-        <v>53400</v>
+        <v>2160</v>
       </c>
       <c r="L18" t="n">
-        <v>53800</v>
+        <v>2475</v>
       </c>
       <c r="M18" t="n">
-        <v>51200</v>
+        <v>2145</v>
       </c>
       <c r="N18" t="n">
-        <v>10.34</v>
+        <v>4.89</v>
       </c>
       <c r="O18" t="n">
-        <v>71872537450</v>
+        <v>47890363022</v>
       </c>
       <c r="P18" t="n">
-        <v>154800</v>
+        <v>4980</v>
       </c>
       <c r="Q18" t="n">
-        <v>51200</v>
+        <v>774</v>
       </c>
       <c r="R18" t="n">
-        <v>-388000</v>
+        <v>-105000</v>
       </c>
       <c r="S18" t="n">
-        <v>-50000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 및 2분기 실적 부진에 대한 실망감. 자사주 매입 및 증권가 전망 언급.</t>
+          <t>로봇 섹터 내 강세 언급 및 주가 흔들림, 개잡주 언급. 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '자사주']</t>
+          <t>['로봇', '기타법인']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F19" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" t="n">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>56907014350</v>
+        <v>57915635860</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 경영진 비판. 상폐 및 부실 기업 의혹 제기.</t>
+          <t>코스피 지수 대비 마이너스, 상폐 및 사기꾼 등 강한 부정적 감정 표출. 객관적 근거 부재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상폐', '경영진']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-4.08%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>14907793342</v>
+        <v>15063168507</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SK하이닉스 관련 호재 언급과 함께 액면병합 가격 및 지수 대비 낮은 주가 움직임에 대한 의문이 제기됩니다.</t>
+          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['액면병합', '자사주 매입', '공매']</t>
+          <t>['SK하이닉스', '공매도', '액면병합']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9050</v>
+        <v>9000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.04%</t>
+          <t>'-5.56%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.83</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" t="n">
         <v>51</v>
@@ -2358,7 +2358,7 @@
         <v>2.63</v>
       </c>
       <c r="O21" t="n">
-        <v>42696492210</v>
+        <v>43091249470</v>
       </c>
       <c r="P21" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_13.xlsx
+++ b/data/trending_integrated_20261028_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151035413646</v>
+        <v>151063809601</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18920</v>
+        <v>18550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.52%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F3" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>321518764195</v>
+        <v>326117339570</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론 등 해외 업체와의 공급망 진입 뉴스 기반, 목표가 상향 및 긍정적 전망.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 관련 뉴스. 글로벌 반도체 공급망 내 입지 강화 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론', '공급망', '반도체']</t>
+          <t>['반도체 장비', '공급망', '뉴스']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27650</v>
+        <v>27750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.42%</t>
+          <t>'+16.84%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>168613015950</v>
+        <v>169444073500</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>188900</v>
+        <v>189900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.40%</t>
+          <t>'+10.99%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>637824134150</v>
+        <v>646191133800</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>우선주 소각 및 실적 발표에 대한 기대감과 함께 외국인 매수세 언급. 긍정적 논조.</t>
+          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주 소각', '실적 발표', '외국인 매수']</t>
+          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1465000</v>
+        <v>1470000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.25%</t>
+          <t>'+9.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G6" t="n">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4188112386500</v>
+        <v>4247797764000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4분기 실적 기대 및 목표 주가 언급, 실적 발표 후에도 상승 전망. 다수 긍정적 기대.</t>
+          <t>4분기 실적 기대감과 저평가 논리에 기반한 매수세 유입 전망. 해외 공급망 관련 뉴스 주목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', '목표주가', '상승']</t>
+          <t>['실적 기대', '저평가', '공급망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14870</v>
+        <v>14970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.54%</t>
+          <t>'+9.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>163385627630</v>
+        <v>164430763515</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>240500</v>
+        <v>240750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.33%</t>
+          <t>'+8.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="G8" t="n">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2817042470750</v>
+        <v>2856739865500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 언급 및 목표가 언급, 공매도 관련 논쟁. 객관적 근거 부족.</t>
+          <t>노무라 증권 목표가 언급 및 개인의 기대감 반영. 다만, 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['성과급', '공매도']</t>
+          <t>['목표가', '기대감', '주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19300</v>
+        <v>18420</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.88%</t>
+          <t>'+7.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>108</v>
+        <v>374</v>
       </c>
       <c r="H9" t="n">
-        <v>4.25</v>
+        <v>4.74</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17890</v>
+        <v>17090</v>
       </c>
       <c r="K9" t="n">
-        <v>18250</v>
+        <v>19270</v>
       </c>
       <c r="L9" t="n">
-        <v>20000</v>
+        <v>20450</v>
       </c>
       <c r="M9" t="n">
-        <v>17950</v>
+        <v>18070</v>
       </c>
       <c r="N9" t="n">
-        <v>3.79</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
-        <v>66693739425</v>
+        <v>45643381140</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>28600</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>11050</v>
       </c>
       <c r="R9" t="n">
-        <v>-23000</v>
+        <v>-55000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
+          <t>AI 데이터센터 방열 시스템 공급 계약 체결 및 휴머노이드 로봇 관련 호재. 글로벌 대호재 2개 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['AI 데이터센터', '로봇', '공급 계약']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18340</v>
+        <v>19040</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.31%</t>
+          <t>'+6.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="H10" t="n">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17090</v>
+        <v>17890</v>
       </c>
       <c r="K10" t="n">
-        <v>19270</v>
+        <v>18250</v>
       </c>
       <c r="L10" t="n">
-        <v>20450</v>
+        <v>20000</v>
       </c>
       <c r="M10" t="n">
-        <v>18070</v>
+        <v>17950</v>
       </c>
       <c r="N10" t="n">
-        <v>4.13</v>
+        <v>3.79</v>
       </c>
       <c r="O10" t="n">
-        <v>45465208445</v>
+        <v>67770860205</v>
       </c>
       <c r="P10" t="n">
-        <v>28600</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>11050</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-55000</v>
+        <v>-23000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>나무가의 로봇 및 AI 관련 사업 기대감 상승. 미국 휴머노이드 폭등, 로봇의 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 긍정적 뉴스 다수 확인.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['휴머노이드', 'AI', '로봇']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8730</v>
+        <v>2597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.46%</t>
+          <t>'+6.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8200</v>
+        <v>2450</v>
       </c>
       <c r="K11" t="n">
-        <v>8230</v>
+        <v>2525</v>
       </c>
       <c r="L11" t="n">
-        <v>9780</v>
+        <v>2965</v>
       </c>
       <c r="M11" t="n">
-        <v>8100</v>
+        <v>2505</v>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>119354198525</v>
+        <v>83963007965</v>
       </c>
       <c r="P11" t="n">
-        <v>9820</v>
+        <v>2965</v>
       </c>
       <c r="Q11" t="n">
-        <v>2965</v>
+        <v>865</v>
       </c>
       <c r="R11" t="n">
-        <v>-67000</v>
+        <v>-365000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
+          <t>거래량 증가 및 개인 물량 흡수 기반 반등 기대. 전환사채 및 전환 이슈 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '테마']</t>
+          <t>['거래량', '반등 기대', '전환사채']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2600</v>
+        <v>8670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+6.12%</t>
+          <t>'+5.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="H12" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2450</v>
+        <v>8200</v>
       </c>
       <c r="K12" t="n">
-        <v>2525</v>
+        <v>8230</v>
       </c>
       <c r="L12" t="n">
+        <v>9780</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>120479144325</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9820</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2965</v>
       </c>
-      <c r="M12" t="n">
-        <v>2505</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O12" t="n">
-        <v>83539941916</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2965</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>865</v>
-      </c>
       <c r="R12" t="n">
-        <v>-365000</v>
+        <v>-67000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 개인 물량 흡수하며 2750원, 3000원 돌파 기대감. 시세 분출 기간 진입 전망.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['거래량', '개인 물량 흡수', '시세 분출']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64400</v>
+        <v>64600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+3.86%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>208068656500</v>
+        <v>210630442000</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>180400</v>
+        <v>179500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.50%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>686</v>
+        <v>719</v>
       </c>
       <c r="F14" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="G14" t="n">
-        <v>2420</v>
+        <v>2500</v>
       </c>
       <c r="H14" t="n">
         <v>35.43</v>
@@ -1708,13 +1708,13 @@
         <v>186900</v>
       </c>
       <c r="M14" t="n">
-        <v>180000</v>
+        <v>179300</v>
       </c>
       <c r="N14" t="n">
         <v>35.49</v>
       </c>
       <c r="O14" t="n">
-        <v>135913647950</v>
+        <v>142492231450</v>
       </c>
       <c r="P14" t="n">
         <v>304000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>지수 대비 낮은 상승률, 외인/연기금 매도 및 공매도 비율 지적. 부정적 논조.</t>
+          <t>호재에도 불구하고 약세 지속. 외인, 연기금 매도 및 공매도 비율 증가로 인한 하락 압력.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '외인매도']</t>
+          <t>['약세', '외인 매도', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>29503584175</v>
+        <v>29833940650</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1855,18 +1855,18 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16480</v>
+        <v>16500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F16" t="n">
         <v>89</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>48039434055</v>
+        <v>49792638720</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1958,13 +1958,13 @@
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="F17" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G17" t="n">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>74616518850</v>
+        <v>75710628300</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2145</v>
+        <v>14230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="G18" t="n">
-        <v>279</v>
+        <v>584</v>
       </c>
       <c r="H18" t="n">
-        <v>5.07</v>
+        <v>9.83</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2170</v>
+        <v>14450</v>
       </c>
       <c r="K18" t="n">
-        <v>2160</v>
+        <v>14750</v>
       </c>
       <c r="L18" t="n">
-        <v>2475</v>
+        <v>14870</v>
       </c>
       <c r="M18" t="n">
-        <v>2145</v>
+        <v>14090</v>
       </c>
       <c r="N18" t="n">
-        <v>4.89</v>
+        <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>47890363022</v>
+        <v>58683291705</v>
       </c>
       <c r="P18" t="n">
-        <v>4980</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>774</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-105000</v>
+        <v>-873000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-85000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>로봇 섹터 내 강세 언급 및 주가 흔들림, 개잡주 언급. 객관적 근거 부족.</t>
+          <t>코스피 지수 대비 마이너스, 상폐 및 사기꾼 등 강한 부정적 감정 표출. 객관적 근거 부재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['로봇', '기타법인']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14240</v>
+        <v>2125</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.19</v>
+        <v>0.18</v>
       </c>
       <c r="E19" t="n">
-        <v>248</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>574</v>
+        <v>300</v>
       </c>
       <c r="H19" t="n">
-        <v>9.83</v>
+        <v>5.07</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14450</v>
+        <v>2170</v>
       </c>
       <c r="K19" t="n">
-        <v>14750</v>
+        <v>2160</v>
       </c>
       <c r="L19" t="n">
-        <v>14870</v>
+        <v>2475</v>
       </c>
       <c r="M19" t="n">
-        <v>14090</v>
+        <v>2125</v>
       </c>
       <c r="N19" t="n">
-        <v>10.02</v>
+        <v>4.89</v>
       </c>
       <c r="O19" t="n">
-        <v>57915635860</v>
+        <v>48518723626</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>4980</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>774</v>
       </c>
       <c r="R19" t="n">
-        <v>-873000</v>
+        <v>-105000</v>
       </c>
       <c r="S19" t="n">
-        <v>-85000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>코스피 지수 대비 마이너스, 상폐 및 사기꾼 등 강한 부정적 감정 표출. 객관적 근거 부재.</t>
+          <t>로봇 섹터 강세에도 불구하고 주가 흐름 둔화. 보호예수 해제 및 불확실성 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['로봇 섹터', '보호예수', '주가 흐름']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>15063168507</v>
+        <v>15144310877</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9000</v>
+        <v>9030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.56%</t>
+          <t>'-5.25%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.83</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
         <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H21" t="n">
         <v>3.46</v>
@@ -2358,7 +2358,7 @@
         <v>2.63</v>
       </c>
       <c r="O21" t="n">
-        <v>43091249470</v>
+        <v>43322310490</v>
       </c>
       <c r="P21" t="n">
         <v>11690</v>
